--- a/downloads/daily/n01-let.xlsx
+++ b/downloads/daily/n01-let.xlsx
@@ -512,7 +512,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>1. Dùng =LET(ty_le,B2, doanh,C2, doanh*ty_le).</t>
+          <t>1. Dùng =LET(ty_le,B5, doanh,C5, doanh*ty_le) cho dòng dữ liệu đầu tiên.</t>
         </is>
       </c>
     </row>
